--- a/docs/AlphaFlow_Endelig-Tjekliste.xlsx
+++ b/docs/AlphaFlow_Endelig-Tjekliste.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,8 +86,96 @@
       <color rgb="00595959"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF2F5496"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF2F5496"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF9C6500"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF9C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF9C6500"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF9C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -119,8 +207,38 @@
         <fgColor rgb="002F5496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F5496"/>
+        <bgColor rgb="FF2F5496"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -142,11 +260,17 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -188,6 +312,52 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -550,35 +720,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF2F5496"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>AlphaFlow — Tjekliste til anmeldelse af bogføringssystem</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Om AlphaFlow</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>AlphaFlow er et cloud-baseret bogføringssystem (SaaS) udviklet af AlphaAi Consult ApS (CVR 46312058). Systemet er bygget med Next.js, TypeScript og Prisma ORM og kører på Neon PostgreSQL (EU) med Caddy reverse proxy, TLS 1.2/1.3 og PM2 proces-håndtering på IONOS VPS (EU/Tyskland).
 Denne tjekliste er AlphaFlows svar på Erhvervsstyrelsens tjekliste for anmeldelse af standard bogføringssystemer. Hvert krav er vurderet som Opfyldt (Ja), Delvist opfyldt (Delvist), Ikke opfyldt (Nej) eller Ikke relevant.</t>
@@ -589,43 +760,43 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8"/>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>Lovgrundlag</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>Lov om bogføring (LOV nr. 700 af 24. maj 2022)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>BEK nr. 97 af 26. januar 2023 — Kravbekendtgørelsen (krav til systemerne: §3 5-års, §7 backup, §8 stk. 4 IT-sikkerhedshovedkrav, Bilag 1 bogføringskrav, Bilag 2 automatiseringskrav)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>BEK nr. 98 af 26. januar 2023 — Anmeldelsesbekendtgørelsen (anmeldelse og registrering; BEK 98 §1 henviser til BEK 97)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Dokumentationshenvisninger — vigtigt</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>Alle henvisninger i kolonnen 'Henvisning til dokumentation/bilag' angiver et navngivet, nummereret bilag og et konkret afsnit, f.eks. 'Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.4'. Erhvervsstyrelsen accepterer ikke links eller kildefilstier som dokumentation.
 Bilag 1–12 og 19 udgør den skriftlige dokumentation (markdown i docs-mappen, konverteres til PDF ved indsendelse). Bilag 13–18 er underskrevne underbehandler-DPA'er, der vedhæftes som separate PDF-filer ved indsendelsen via virk.dk. Se Bilag 12 (BILAG_OVERSIGT.md) for den komplette bilagsliste.
@@ -638,56 +809,57 @@
     <row r="18"/>
     <row r="19"/>
     <row r="20"/>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>Farvekoder</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>Ja (Opfyldt)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>Delvist opfyldt</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t>Nej (Ikke opfyldt)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>Ikke relevant</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t>Version: 2.0 — 2026 (revideret med præcise dokumentationshenvisninger efter Erhvervsstyrelsens svar i sagen)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A16:E20"/>
     <mergeCell ref="A4:E8"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A22:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -696,591 +868,592 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF2F5496"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="53" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>Krav</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>Bkg.</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="29" t="inlineStr">
         <is>
           <t>Opfyldt?</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>Beskrivelse</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>Henvisning til dokumentation/bilag</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="29" t="inlineStr">
         <is>
           <t>Teknisk kilde (supplerende, ikke dokumentation)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>Navn</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 1, nr. 1</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D2" s="30" t="inlineStr">
         <is>
           <t>AlphaFlow er udviklet af AlphaAi Consult ApS. Ansøgeroplysninger angives via virk.dk ved indsendelse.</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="30" t="inlineStr">
         <is>
           <t>Bilag 5 (DATABEHANDLERAFTALE.md) afsnit 1.1 (parter) og afsnit 13 (revisionsret). Navn angives via virk.dk.</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="30" t="inlineStr">
         <is>
           <t>docs/ANMELDELSESPAKKE.md afsnit 2</t>
         </is>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>CVR-nr.</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 1, nr. 1</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D3" s="30" t="inlineStr">
         <is>
           <t>AlphaAi Consult ApS, CVR 46312058. Angives via virk.dk ved indsendelse.</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 18.2 (CVR 46312058). Angives via virk.dk.</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>Adresse</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 1, nr. 2</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>Skelagervej 124C, 8200 Aarhus N. Angives via virk.dk.</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 18.2. Angives via virk.dk.</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>E-mail</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 1, nr. 2</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D5" s="30" t="inlineStr">
         <is>
           <t>Kontakt-e-mail angives via virk.dk ved indsendelse.</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="30" t="inlineStr">
         <is>
           <t>Angives via virk.dk.</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>Navn på kontaktperson</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 1, nr. 3</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>Kontaktperson angives via virk.dk ved indsendelse.</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>Angives via virk.dk.</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>Sprog</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>§ 3, stk. 2</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>Brugergrænseflade og dokumentation er på dansk (DA/EN sprogvalg i UI).</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 3.6 (sprog DA/EN). Dokumentationen Bilag 1–12 er på dansk.</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="30" t="inlineStr">
         <is>
           <t>src/lib/language-store.ts</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>Bogføringssystemets navn</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 1, nr. 4</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>AlphaFlow — distinkt navn.</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>Bilag 1 (ANMELDELSESPAKKE.md) afsnit 2 (ansøgeroplysninger) og afsnit 3 (produktbeskrivelse).</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>Cloud-baseret eller hybridt</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 1, nr. 5</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>Cloud-baseret SaaS (ikke hybridt). Hosting på Neon PostgreSQL (EU) + IONOS VPS (EU/Tyskland).</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 1.4 (platformens omfang) og afsnit 8 (netværkssikkerhed). Bilag 9 (NEON &amp; IONOS_IT_SIKKERHED.md) afsnit 2.</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="30" t="inlineStr">
         <is>
           <t>Caddyfile; ecosystem.config.example.js</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>Moduler/udvidelser</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 1, nr. 6</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>Intet tredjeparts modul-/udvidelsessystem. Funksjonalitet er indbygget.</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>Bilag 1 (ANMELDELSESPAKKE.md) afsnit 3 (produktbeskrivelse).</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>Opbevaringsvirksomhed CVR</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 1, nr. 7</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>Opbevaring hos Neon, Inc. (database) og IONOS SE (VPS + backup). Begge EU-baserede.</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>Bilag 9 (NEON &amp; IONOS_IT_SIKKERHED.md) afsnit 3 (Neon) og afsnit 4 (IONOS). DPA'er: Bilag 13 (Neon) og Bilag 14 (IONOS) — separate PDF'er ved indsendelse. Se Bilag 12 (BILAG_OVERSIGT.md) afsnit 3.</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>docs/LEVERANDØERSTYRING.md afsnit 3.1–3.2</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>Beskrivelse af § 15 opfyldelse</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 2, nr. 1</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="inlineStr">
         <is>
           <t>Beskrivelse af opfyldelse af Lov om bogføring §15 (krav til digitale systemer) via BEK 97 §3 (5-års) og §7 (backup).</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.4 (backup og 5-års opbevaring) + Bilag 3 (ENCRYPTION.md) afsnit 6.4 (retention 60 mdr) + Bilag 7 (BEREDSKABSPLAN.md) afsnit 4 (backup-strategi).</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="30" t="inlineStr">
         <is>
           <t>src/lib/backup-scheduler.ts; src/lib/backup-engine.ts</t>
         </is>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>Modul/udvidelse beskrivelse</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 2, nr. 2</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t>Ikke relevant</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>Intet tredjeparts modul-system.</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>N/A (intet modul-system)</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>Beskrivelse af § 9 opfyldelse</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 2, nr. 3</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D14" s="30" t="inlineStr">
         <is>
           <t>Risikovurdering jf. BEK 97 §8 stk. 2 (CIA-triaden) er dokumenteret.</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>Bilag 6 (RISIKOVURDERING.md) afsnit 1–7 (risikovurdering) + Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 10 (mangler og afhjælpning).</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="30" t="inlineStr">
         <is>
           <t>docs/RISIKOVURDERING.md</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>Databehandleraftale</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 2, nr. 4</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>Hoved-DPA mellem AlphaAi Consult ApS (databehandler) og kunden (dataansvarlig) samt underbehandler-DPA'er.</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>Bilag 5 (DATABEHANDLERAFTALE.md) — hoved-DPA. Underbehandler-DPA'er: Bilag 13–20 (separate PDF'er) — oversigt i Bilag 12 (BILAG_OVERSIGT.md) afsnit 3.</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="30" t="inlineStr">
         <is>
           <t>docs/LEVERANDØERSTYRING.md</t>
         </is>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>Aftale med 3.part opbevaring</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 2, nr. 5</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
         <is>
           <t>Aftaler med Neon (database) og IONOS (VPS/backup) for opbevaring.</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>Bilag 9 (NEON &amp; IONOS_IT_SIKKERHED.md) afsnit 3 (Neon) og afsnit 4 (IONOS). DPA'er: Bilag 13 (Neon) + Bilag 14 (IONOS) — separate PDF'er. Underbehandlerliste: Bilag 8 (LEVERANDØERSTYRING.md) afsnit 3.</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="30" t="inlineStr">
         <is>
           <t>docs/DATABEHANDLERAFTALE.md afsnit 5</t>
         </is>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>Midlertidig adgang</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 3</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
         <is>
           <t>Midlertidig adgang (revisor, oversight) via RBAC + revisionsret jf. GDPR Art. 28(3)(h).</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 4.3 (RBAC) + Bilag 5 (DATABEHANDLERAFTALE.md) afsnit 13 (revisionsret) og afsnit 9 (tredjelande).</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="30" t="inlineStr">
         <is>
           <t>src/lib/rbac.ts; src/lib/route-guard.ts</t>
         </is>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>It-sikkerhed niveau</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>§ 13</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D18" s="30" t="inlineStr">
         <is>
           <t>It-sikkerhedsniveau dokumenteret i særskilte bilag (BEK 97 §8 stk. 4 hovedkrav).</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>Bilag 3 (ENCRYPTION.md) + Bilag 6 (RISIKOVURDERING.md) + Bilag 7 (BEREDSKABSPLAN.md) + Bilag 8 (LEVERANDØERSTYRING.md). Samlet i Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 4–9.</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="30" t="inlineStr">
         <is>
           <t>Caddyfile; next.config.ts; src/lib/crypto.ts</t>
         </is>
@@ -1294,6 +1467,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1301,7 +1475,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
@@ -1309,667 +1483,667 @@
     <col width="38" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>Krav</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>Bkg.</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="29" t="inlineStr">
         <is>
           <t>Vejl.</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>Opfyldt?</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>Beskrivelse</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="29" t="inlineStr">
         <is>
           <t>Henvisning til dokumentation/bilag</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="29" t="inlineStr">
         <is>
           <t>Teknisk kilde (supplerende, ikke dokumentation)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>Transaktionsdato</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>Bilag 1, 1, a</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D2" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="C2" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E2" s="30" t="inlineStr">
         <is>
           <t>Transaktionsdato registreres på hver postering/journalpost.</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 5.2 (finansjournal) + Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1 (systemegnethed).</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="30" t="inlineStr">
         <is>
           <t>prisma/schema.prisma (Transaction/JournalEntry.date); src/app/api/transactions/route.ts; src/app/api/journal-entries/route.ts</t>
         </is>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>Beløb</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>Bilag 1, 1, b</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="C3" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t>Beløb registreres (debet/kredit) med balance-validering.</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1 + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 5.2.</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t>prisma/schema.prisma; src/app/api/journal-entries/route.ts</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>Bilagsnummer</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Bilag 1, 1, c</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>Fortløbende bilagsnummer (BIL-ÅÅÅÅ-NNNN) via journalPrefix + nextJournalSequence.</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.5 (fortløbende bilagsnummerering) + Bilag 4 afsnit 5.3 + Bilag 10 (UDBEDRINGSPLAN.md) afsnit 4 (mangel 3).</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t>src/lib/voucher-number.ts; prisma/schema.prisma (Company.journalPrefix)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>Transaktionstekst</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>Bilag 1, 1, d</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E5" s="30" t="inlineStr">
         <is>
           <t>Beskrivelse/tekst på hver postering.</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1 + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 5.2.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="30" t="inlineStr">
         <is>
           <t>prisma/schema.prisma (description); src/app/api/journal-entries/route.ts</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>Valutakurs/omregningsfaktor</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Bilag 1, 1, e</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>Valuta med kurs og DKK-omregning (Frankfurter/ECB API).</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1 (valutahåndtering) + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 5.5 (multi-currency).</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="30" t="inlineStr">
         <is>
           <t>src/lib/currency-utils.ts; src/app/api/exchange-rate/route.ts</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>Registreringsdato</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Bilag 1, 2, a</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>Registreringsdato (createdAt) registreres automatisk.</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 6.2 (AuditLog.createdAt) + afsnit 2.1.</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="30" t="inlineStr">
         <is>
           <t>prisma/schema.prisma (createdAt)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>Fortløbende transaktionsnummer</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>Bilag 1, 2, b</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>Fortløbende nummerering pr. tenant, atomisk i DB-transaktion.</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.5 + Bilag 10 (UDBEDRINGSPLAN.md) afsnit 4 (mangel 3 — voucherNumber). Bemærk: afventer db:push på produktions-VPS, jf. Bilag 10 afsnit 8.6.</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t>src/lib/voucher-number.ts; src/app/api/journal-entries/route.ts; src/app/api/invoices/route.ts</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>Initialer for bogfører</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Bilag 1, 2, c</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>Bogfører-identitet (userId) registreres via AuditLog.</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 6.2 (AuditLog userId) + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 5.2.</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="30" t="inlineStr">
         <is>
           <t>src/lib/audit.ts; src/app/api/journal-entries/route.ts</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>Ændringer gemmes</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Bilag 1, 2, d</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>Alle ændringer logges uforanderligt i AuditLog (CREATE-only).</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 6 (audit og logning) + Bilag 3 (ENCRYPTION.md) afsnit 3.9 (immutability).</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="30" t="inlineStr">
         <is>
           <t>src/lib/audit.ts</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>Kan ikke ændres/slettes</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Bilag 1, 2, e</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Delvist</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>Bogførte posteringer kan ikke hard-slettes via API; kun annullering med modpost. MEN: ingen kryptografisk hash-chain — posteringer kan teknisk muteres direkte i DB uden hash-detektion. AuditLog er derimod 3-niveau uforanderlig.</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.3 (uforanderlighed) + Bilag 3 (ENCRYPTION.md) afsnit 3.9 + Bilag 6 (RISIKOVURDERING.md) R-04 (restrisiko). Delvist: jf. Bilag 10 (UDBEDRINGSPLAN.md) og Bilag 1 (ANMELDELSESPAKKE.md) afsnit 8 punkt 10.</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t>src/lib/audit.ts; prisma/audit-immutability.sql; src/app/api/journal-entries/[id]/route.ts</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>Købsbilag opbevares digitalt</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Bilag 1, 3, a</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>Købsbilag uploades og opbevares digitalt (MIME-whitelist, max 25 MB).</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 5.11 (bilagsvedhæftning) + Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 9 (fil-upload sikkerhed).</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="30" t="inlineStr">
         <is>
           <t>src/app/api/documents/route.ts; src/lib/ocr/</t>
         </is>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>Salgsbilag opbevares digitalt</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Bilag 1, 3, b</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>Salgsfaktura-PDF og OIOUBL-XML genereres og opbevares.</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 6.3 (PDF og e-mail) + Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1.</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="30" t="inlineStr">
         <is>
           <t>src/app/api/invoices/[id]/pdf/route.ts; src/lib/oioubl-generator.ts</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>5-års opbevaring</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Bilag 1, 4</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>Månedsbackup retention 60 måneder = 5 år (BEK 97 §3).</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.4 (backup og 5-års) + Bilag 3 (ENCRYPTION.md) afsnit 6.4 (retention) + Bilag 7 (BEREDSKABSPLAN.md) afsnit 4.</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="30" t="inlineStr">
         <is>
           <t>src/lib/backup-scheduler.ts; src/lib/backup-engine.ts (RETENTION.monthly=60)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>Bevares uændret</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Bilag 1, 4, a</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>Delvist</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>Bogføringsmaterialet bevares via uforanderlig AuditLog + DB-triggere. MEN: ingen kryptografisk hash-chain på posteringer (jf. R-04).</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.3 + Bilag 3 (ENCRYPTION.md) afsnit 3.9 + Bilag 6 (RISIKOVURDERING.md) R-04. Delvist: jf. Bilag 1 afsnit 8 punkt 10.</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="30" t="inlineStr">
         <is>
           <t>src/lib/audit.ts; prisma/audit-immutability.sql</t>
         </is>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>Struktureret maskinlæsbart format 5 år</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>Bilag 1, 4, b</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>SAF-T Financial DK v1.0 XML-eksport + tenant-eksport (JSON + filer).</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.7 (SAF-T) og afsnit 2.9 (udbyderskift) + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 10.8.</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="30" t="inlineStr">
         <is>
           <t>src/app/api/export-saft/route.ts; src/lib/saft-validator.ts; src/app/api/export-tenant/route.ts</t>
         </is>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>Bilag opbevares 5 år ved skift</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>Bilag 1, 4, c</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>Ved udbyderskift eksporteres alle data + filer (SHA-256 manifest) til anden udbyder.</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.9 (udbyderskift) + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 15.2–15.3 (eksport + providerswitch).</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="30" t="inlineStr">
         <is>
           <t>src/app/api/export-tenant/route.ts; src/app/api/import-tenant/route.ts; src/app/api/export-saft/route.ts</t>
         </is>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>Krypterede data kan dekrypteres</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Bilag 1, 4, d</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>AES-256-GCM-krypteret data (bank-tokens, TOTP, backup) kan dekrypteres med ENCRYPTION_KEY. Tabt nøgle = permanent datatab.</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="30" t="inlineStr">
         <is>
           <t>Bilag 3 (ENCRYPTION.md) afsnit 3.1 (AES-256-GCM) + afsnit 7 (implementering) + afsnit 2.4 (nøglehåndtering — tabt nøgle = datatab).</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="30" t="inlineStr">
         <is>
           <t>src/lib/crypto.ts</t>
         </is>
@@ -1983,756 +2157,757 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFBF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>Krav</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>Bkg.</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="29" t="inlineStr">
         <is>
           <t>Vejl.</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>Opfyldt?</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>Beskrivelse</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="29" t="inlineStr">
         <is>
           <t>Henvisning til dokumentation/bilag</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="29" t="inlineStr">
         <is>
           <t>Teknisk kilde (supplerende, ikke dokumentation)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>Netværkssikkerhed</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 4, nr. 1</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="30" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="D2" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E2" s="30" t="inlineStr">
         <is>
           <t>TLS 1.2/1.3 via Caddy + security headers + DB sslmode=require.</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="30" t="inlineStr">
         <is>
           <t>Bilag 3 (ENCRYPTION.md) afsnit 4 (data-in-transit/TLS) + Bilag 9 (NEON &amp; IONOS_IT_SIKKERHED.md) afsnit 5 (Caddy) og afsnit 6 (netværk).</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="30" t="inlineStr">
         <is>
           <t>Caddyfile; src/lib/db.ts (sslmode=require)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>Adgangsstyring</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 4, nr. 2</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="30" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="D3" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t>RBAC (5 roller/23 permissions) + TOTP 2FA + bcrypt + rate-limiting.</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 4 (adgangskontrol og identitet) + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 2.4 (2FA) og afsnit 4 (roller).</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t>src/lib/rbac.ts; src/lib/two-factor.ts; src/lib/password.ts; src/app/api/auth/2fa/</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>Leverandørstyring</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 4, nr. 3</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>Due diligence + løbende overvågning af underbehandlere + DPA'er.</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="30" t="inlineStr">
         <is>
           <t>Bilag 8 (LEVERANDØERSTYRING.md) + Bilag 12 (BILAG_OVERSIGT.md) afsnit 3 (DPA-bilag 13–20).</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t>docs/LEVERANDØERSTYRING.md</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>Backup (daglig inkrementel, ugentlig fuld)</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>§§ 7 og 8, stk. 4, nr. 4</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E5" s="30" t="inlineStr">
         <is>
           <t>node-cron scheduler: hourly/daily/weekly/monthly + AES-256-GCM .zip.enc + SHA-256.</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.4 + Bilag 3 (ENCRYPTION.md) afsnit 6.4 + Bilag 7 (BEREDSKABSPLAN.md) afsnit 4 (backup-strategi) og afsnit 5 (gendannelse).</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="30" t="inlineStr">
         <is>
           <t>src/lib/backup-scheduler.ts; src/lib/backup-engine.ts</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>Logning</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 4, nr. 5</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>Uforanderlig AuditLog (21 action-typer, 25 entity-typer, 72+ ruter).</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 6 (audit og logning) + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 17.1 (revisionslog).</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="30" t="inlineStr">
         <is>
           <t>src/lib/audit.ts; Caddyfile (access-log)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>Beredskab og reetablering</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 4, nr. 6</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>DR-plan med RTO/RPO, 8 gendannelsesscenarier, incident response.</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="30" t="inlineStr">
         <is>
           <t>Bilag 7 (BEREDSKABSPLAN.md) — afsnit 3 (RTO/RPO), afsnit 5 (gendannelse), afsnit 6 (incident response).</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="30" t="inlineStr">
         <is>
           <t>docs/BEREDSKABSPLAN.md; src/lib/backup-engine.ts</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>Databeskyttelse</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 4, nr. 7</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>Kryptering (AES-256-GCM, bcrypt, TLS) + GDPR-overholdelse.</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>Bilag 3 (ENCRYPTION.md) + Bilag 5 (DATABEHANDLERAFTALE.md) + Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 3 (GDPR) og afsnit 5 (kryptering).</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t>src/lib/crypto.ts</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>Tredjeparts IT-sikkerhed</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 6</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>N23</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>IT-sikkerhedsdokumentation for Neon og IONOS (infrastruktur).</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="30" t="inlineStr">
         <is>
           <t>Bilag 9 (NEON &amp; IONOS_IT_SIKKERHED.md) + Bilag 8 (LEVERANDØERSTYRING.md) afsnit 3.</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="30" t="inlineStr">
         <is>
           <t>docs/NEON &amp; IONOS_IT_SIKKERHED.md</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>Databehandleraftale</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>BEK 98 § 8, stk. 2, nr. 5</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>Hoved-DPA + underbehandler-DPA'er.</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="30" t="inlineStr">
         <is>
           <t>Bilag 5 (DATABEHANDLERAFTALE.md) — hoved-DPA. Underbehandler-DPA'er: Bilag 13–20 (separate PDF'er) — oversigt i Bilag 12 afsnit 3.</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="30" t="inlineStr">
         <is>
           <t>docs/DATABEHANDLERAFTALE.md</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>Aftale med 3.part</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>BEK 98 § 8, stk. 2, nr. 5</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>DPA med Neon (database) og IONOS (VPS/backup).</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>Bilag 9 (NEON &amp; IONOS_IT_SIKKERHED.md) afsnit 3–4 + Bilag 5 (DATABEHANDLERAFTALE.md) afsnit 5 (underbehandlere) + Bilag 13–14 (Neon/IONOS DPA, separate PDF'er).</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t>docs/DATABEHANDLERAFTALE.md afsnit 5</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>Risikovurdering omfatter tab af tilgængelighed etc.</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 2</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>Risikovurdering dækker CIA-triaden (tilgængelighed, integritet, fortrolighed).</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="30" t="inlineStr">
         <is>
           <t>Bilag 6 (RISIKOVURDERING.md) afsnit 5 (risici R-01..R-20) + afsnit 1.2 (BEK 97 §8 stk. 2 CIA-triaden).</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="30" t="inlineStr">
         <is>
           <t>docs/RISIKOVURDERING.md</t>
         </is>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>Tager hensyn til tredjeparter</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 2</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>Risikovurdering inkluderer underbehandlere (Neon, IONOS, USA AI-udbydere).</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="30" t="inlineStr">
         <is>
           <t>Bilag 6 (RISIKOVURDERING.md) afsnit 4 (aktiver og sårbarheder) + Bilag 8 (LEVERANDØERSTYRING.md) afsnit 6 (løbende overvågning).</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="30" t="inlineStr">
         <is>
           <t>docs/RISIKOVURDERING.md afsnit 4</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>Løbende opdatering ved trusselsændringer</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 2</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>Årlig review + ved trusselsændringer/udbyderændringer.</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="30" t="inlineStr">
         <is>
           <t>Bilag 6 (RISIKOVURDERING.md) afsnit 8.3 (overvågning) + Bilag 8 (LEVERANDØERSTYRING.md) afsnit 4 (due diligence) og afsnit 6 (overvågning).</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="30" t="inlineStr">
         <is>
           <t>docs/RISIKOVURDERING.md afsnit 8</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>Konsekvens- og sandsynlighedsvurdering</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>ISO 27005-metodologi med sandsynligheds- og konsekvensskalaer + risikomatrix.</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="30" t="inlineStr">
         <is>
           <t>Bilag 6 (RISIKOVURDERING.md) afsnit 1.3–1.4 (metodologi/skalaer) + afsnit 5 (risici) + afsnit 6 (matrix).</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="30" t="inlineStr">
         <is>
           <t>docs/RISIKOVURDERING.md</t>
         </is>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>Hændelig/ulovlig tilintetgørelse</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 3, nr. 1</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>Immutability (AuditLog 3-niveau) + backup (AES-256-GCM) + gendannelse.</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.3 (immutability) + Bilag 6 (RISIKOVURDERING.md) R-01..R-04 + Bilag 7 (BEREDSKABSPLAN.md) afsnit 5 (gendannelse).</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="30" t="inlineStr">
         <is>
           <t>prisma/schema.prisma; src/lib/audit.ts; prisma/audit-immutability.sql; src/lib/backup-engine.ts</t>
         </is>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>Uberettigede ændringer/uautoriseret adgang</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 3, nr. 1</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>RBAC + 2FA + audit-log + kryptering + rate-limiting.</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 4 (adgangskontrol) + afsnit 6 (audit) + Bilag 3 (ENCRYPTION.md) + Bilag 6 (RISIKOVURDERING.md) R-05..R-09.</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="30" t="inlineStr">
         <is>
           <t>src/lib/rbac.ts; src/lib/two-factor.ts; src/lib/audit.ts; src/lib/crypto.ts; src/lib/rate-limit.ts</t>
         </is>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>Behandling af persondata/databehandleraftale</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>§ 8, stk. 3, nr. 2</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>DPA + underbehandler-DPA'er + GDPR Art. 28.</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="30" t="inlineStr">
         <is>
           <t>Bilag 5 (DATABEHANDLERAFTALE.md) + Bilag 9 (NEON &amp; IONOS_IT_SIKKERHED.md) afsnit 3–4 + Bilag 12 (BILAG_OVERSIGT.md) afsnit 3 (DPA-bilag 13–20).</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="30" t="inlineStr">
         <is>
           <t>docs/DATABEHANDLERAFTALE.md</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>Backup opbevares under IT-sikkerhed</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>§ 7, stk. 2</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E19" s="30" t="inlineStr">
         <is>
           <t>Backup-filer er AES-256-GCM-krypteret (.zip.enc) + SHA-256 checksum + adgangskontrol på VPS.</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="30" t="inlineStr">
         <is>
           <t>Bilag 3 (ENCRYPTION.md) afsnit 6.1 + 6.4 (backup-kryptering, SHA-256) + Bilag 9 (NEON &amp; IONOS_IT_SIKKERHED.md) afsnit 4.8 (backup-lagring IONOS).</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="30" t="inlineStr">
         <is>
           <t>src/lib/backup-engine.ts (encryptFile, calculateChecksum); src/lib/crypto.ts</t>
         </is>
       </c>
     </row>
     <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>Backup i EU/EØS</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>§ 7, stk. 3</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E20" s="30" t="inlineStr">
         <is>
           <t>Backup lagres på IONOS VPS (EU/Tyskland) + Neon PITR (EU-datacentre).</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="30" t="inlineStr">
         <is>
           <t>Bilag 9 (NEON &amp; IONOS_IT_SIKKERHED.md) afsnit 3 (Neon EU) + afsnit 4 (IONOS EU/Tyskland) + Bilag 13–14 (DPA'er).</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="30" t="inlineStr">
         <is>
           <t>src/lib/backup-engine.ts (BACKUP_BASE_DIR=Tenant-Backup/)</t>
         </is>
@@ -2746,1163 +2921,1164 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFC00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>Krav</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>Bkg.</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="29" t="inlineStr">
         <is>
           <t>Vejl.</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>Opfyldt?</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>Beskrivelse</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="29" t="inlineStr">
         <is>
           <t>Henvisning til dokumentation/bilag</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="29" t="inlineStr">
         <is>
           <t>Teknisk kilde (supplerende, ikke dokumentation)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>Sende faktura i OIOUBL</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 1, a</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D2" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="C2" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E2" s="30" t="inlineStr">
         <is>
           <t>OIOUBL 2.1 (type 380) via Storecove/NemHandel.</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1 (e-fakturering) + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 6.4 (send e-faktura).</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="30" t="inlineStr">
         <is>
           <t>src/lib/oioubl-generator.ts; src/app/api/invoices/[id]/oioubl/route.ts; src/lib/einvoice-sender.ts; src/lib/nemhandel-client.ts</t>
         </is>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>Modtage faktura i OIOUBL</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 1, b</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="C3" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t>Modtagelse via e-faktura-indbakke (OIOUBL parser).</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1 + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 6.6 (e-faktura indbakke).</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t>src/lib/einvoice-parser.ts; src/app/api/invoices/receive/route.ts; src/components/invoices/einvoice-inbox.tsx</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>Sende kreditnota i OIOUBL</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 1, c</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>Delvist</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>OIOUBL-generator understøtter type 381, MEN der er intet oprettelses-flow i UI, og einvoice-sender hardcoder type 380. Kreditnota kan derfor ikke reelt sendes.</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1 + Bilag 1 (ANMELDELSESPAKKE.md) afsnit 8 punkt 11 + Bilag 10 (UDBEDRINGSPLAN.md). Delvist: biblioteket kan generere 381, men ingen afsendelse/oprettelse.</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t>src/lib/oioubl-generator.ts (type 381); src/app/api/invoices/[id]/oioubl/route.ts; src/lib/einvoice-sender.ts (hardcoder 380)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>Modtage kreditnota i OIOUBL</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 1, d</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E5" s="30" t="inlineStr">
         <is>
           <t>Parser understøtter modtagelse af type 381 (kreditnota).</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 6.6 (e-faktura indbakke — parser understøtter 381).</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="30" t="inlineStr">
         <is>
           <t>src/lib/einvoice-parser.ts; src/app/api/invoices/receive/route.ts</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>Application response ved OIOUBL</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 1, e</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>ApplicationResponse genereres ved modtagelse.</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1 + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 6.6.</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="30" t="inlineStr">
         <is>
           <t>src/lib/einvoice-response.ts; src/app/api/invoices/receive/route.ts</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>Sende faktura i Peppol BIS</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 2, a</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>Peppol BIS Billing 3.0 via Storecove Access Point.</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1 + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 6.4.</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="30" t="inlineStr">
         <is>
           <t>src/lib/einvoice-sender.ts; src/lib/nemhandel-client.ts; src/components/invoices/send-einvoice-dialog.tsx</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>Modtage faktura i Peppol BIS</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 2, b</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>Modtagelse via e-faktura-indbakke (Peppol BIS parser).</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 6.6.</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t>src/lib/einvoice-parser.ts; src/app/api/invoices/receive/route.ts</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>Sende kreditnota i Peppol BIS</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 2, c</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>Delvist</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>Samme begrænsning som OIOUBL kreditnota — einvoice-sender hardcoder type 380; intet oprettelses-flow.</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1 + Bilag 1 (ANMELDELSESPAKKE.md) afsnit 8 punkt 11 + Bilag 10 (UDBEDRINGSPLAN.md). Delvist.</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="30" t="inlineStr">
         <is>
           <t>src/lib/oioubl-generator.ts; src/lib/einvoice-sender.ts</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>Modtage kreditnota i Peppol BIS</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 2, d</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>Parser understøtter modtagelse af type 381.</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 6.6.</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="30" t="inlineStr">
         <is>
           <t>src/lib/einvoice-parser.ts; src/app/api/invoices/receive/route.ts</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>Message Level Response</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 2, e</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>MessageLevelResponse genereres ved modtagelse.</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1 + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 6.6.</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t>src/lib/einvoice-response.ts; src/app/api/invoices/receive/route.ts</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>Invoice Response</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 2, f</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>InvoiceResponse genereres.</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1 + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 6.6.</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="30" t="inlineStr">
         <is>
           <t>src/lib/einvoice-response.ts</t>
         </is>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>CSV bankimport</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 3, a</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>MT940-fil upload + manuel indtastning af kontoudtog.</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 8.2 (import af kontoudtog) + Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1.</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="30" t="inlineStr">
         <is>
           <t>src/app/api/bank-reconciliation/route.ts</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>Automatisk bankintegration</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 3, b</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>Delvist</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>Tink + Demo er reelle integrationer. Nordea/Danske Bank/Jyske Bank er stubs (returnerer fejl).</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1 (bank) + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 8.1 (bankforbindelser) + Bilag 1 (ANMELDELSESPAKKE.md) afsnit 8 punkt 12 + Bilag 10 (UDBEDRINGSPLAN.md). Delvist: kun Tink + Demo reelle.</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="30" t="inlineStr">
         <is>
           <t>src/app/api/bank-connections/route.ts; src/lib/bank-providers.ts; src/lib/matching-engine.ts</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>PSD2 bankhåndtering</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 3, c</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>Delvist</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>PSD2 consent-flow virker for Tink. Nordea/Danske/Jyske er sandbox-stubs.</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 8.1 (PSD2 consent-flow) + Bilag 1 (ANMELDELSESPAKKE.md) afsnit 8 punkt 12. Delvist: consent virker for Tink; stubs for øvrige banker.</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="30" t="inlineStr">
         <is>
           <t>src/app/api/bank-connections/consent-callback/route.ts; src/app/api/bank-connections/[id]/consent/route.ts</t>
         </is>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>Bankkonto i kontoplan</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 3, 2. afsnit a</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>Bankkonto indgår i FSR-38 kontoplan (standardkonto 5500/5200).</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 5.1 (FSR-38 kontoplan) + Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1.</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="30" t="inlineStr">
         <is>
           <t>src/lib/seed-chart-of-accounts.ts; prisma/schema.prisma</t>
         </is>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>Tydelig difference ved uafstemt</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 3, 2. afsnit b</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>To-panes visning med tydelig Link/Unlink-difference ved uafstemte transaktioner.</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 8.4 (manuel afstemning — to-panes visning).</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="30" t="inlineStr">
         <is>
           <t>src/app/api/bank-reconciliation/route.ts; src/components/bank-reconciliation/bank-reconciliation-page.tsx</t>
         </is>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>Offentlig standardkontoplan direkte</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 4, a</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>SKAT fællesoffentlig standardkontoplan indbygget.</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1 (StandardAccountMapping) + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 5.1.</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="30" t="inlineStr">
         <is>
           <t>src/lib/standard-chart-of-accounts.ts (PUBLIC_STANDARD_CHART)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>Standardkontoplan mappet</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 4, b</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E19" s="30" t="inlineStr">
         <is>
           <t>FSR-38 konti mappet til SKAT standardkontoplan (auto-mapping).</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1 + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 5.1 (StandardMappingPanel).</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="30" t="inlineStr">
         <is>
           <t>src/app/api/accounts/standard-mapping/route.ts; src/lib/standard-chart-of-accounts.ts (buildAutoMapping)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>Mapping-værktøj til standardkontoplan</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 4, c</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E20" s="30" t="inlineStr">
         <is>
           <t>UI-værktøj til manuel/auto-mapping af FSR→standard.</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 5.1 (StandardMappingPanel).</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="30" t="inlineStr">
         <is>
           <t>src/components/chart-of-accounts/standard-mapping-panel.tsx; src/app/api/accounts/standard-mapping/route.ts</t>
         </is>
       </c>
     </row>
     <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>Mapping-værktøj til standardmomskoder</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 4, 2. afsnit a</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E21" s="30" t="inlineStr">
         <is>
           <t>UI-værktøj til mapping af interne momskoder → SKAT momskoder.</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 5.1 (VATMappingPanel) og afsnit 9.1 (momskoder).</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="30" t="inlineStr">
         <is>
           <t>src/lib/standard-chart-of-accounts.ts (VAT_CODE_TO_PUBLIC_MAPPING); src/components/chart-of-accounts/vat-mapping-panel.tsx</t>
         </is>
       </c>
     </row>
     <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>Bogføringsguide/assistent</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 5, a</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="C22" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E22" s="30" t="inlineStr">
         <is>
           <t>PostingGuideAssistant foreslår kontering.</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 5.1 (PostingGuideAssistant).</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="30" t="inlineStr">
         <is>
           <t>src/components/chart-of-accounts/posting-guide-assistant.tsx; src/app/api/accounts/posting-guide/route.ts</t>
         </is>
       </c>
     </row>
     <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t>Konteringsvejledning 3.part</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 5, b</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="C23" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E23" s="30" t="inlineStr">
         <is>
           <t>Standard konteringsvejledning indbygget.</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 5.1.</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G23" s="30" t="inlineStr">
         <is>
           <t>src/components/chart-of-accounts/posting-guide-assistant.tsx</t>
         </is>
       </c>
     </row>
     <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>Brugerdefineret konteringsvejledning</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 5, c</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="C24" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E24" s="30" t="inlineStr">
         <is>
           <t>Bruger kan tilføje egen konteringsvejledning pr. konto.</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 5.1 + Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1.</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="30" t="inlineStr">
         <is>
           <t>src/app/api/accounts/posting-guide/route.ts; prisma/schema.prisma</t>
         </is>
       </c>
     </row>
     <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <t>Standardfil (SAF-T) genereres</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 6, a</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="C25" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E25" s="30" t="inlineStr">
         <is>
           <t>SAF-T Financial DK v1.0 XML med 23+ valideringskontroller.</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.7 (SAF-T) + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 10.8.</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="30" t="inlineStr">
         <is>
           <t>src/app/api/export-saft/route.ts; src/lib/saft-validator.ts</t>
         </is>
       </c>
     </row>
     <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>Standardfil eksporteres til anden udbyder</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 6, b</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="C26" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E26" s="30" t="inlineStr">
         <is>
           <t>Tenant-eksport (JSON + filer + SHA-256 manifest) til anden udbyder.</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.9 (udbyderskift) + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 15.2.</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="30" t="inlineStr">
         <is>
           <t>src/app/api/export-tenant/route.ts; src/app/api/export-saft/route.ts</t>
         </is>
       </c>
     </row>
     <row r="27" ht="60" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>Standardfil kan indlæses</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 6, c</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="C27" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E27" s="30" t="inlineStr">
         <is>
           <t>Tenant-import + restore fra backup-ZIP.</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.9 + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 15.2 og afsnit 14.5 (restore).</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="30" t="inlineStr">
         <is>
           <t>src/app/api/import-tenant/route.ts; src/app/api/backups/upload-restore/route.ts</t>
         </is>
       </c>
     </row>
     <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>CSV/XBRL til årsregnskab</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 7, a</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="C28" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E28" s="30" t="inlineStr">
         <is>
           <t>Årsrapport i CSV (Regnskab Basis) og iXBRL (Regnskab Special, DCCA taxonomy).</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.8 (årsrapport CSV/iXBRL) + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 10.9.</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="30" t="inlineStr">
         <is>
           <t>src/app/api/reports/annual-csv/route.ts; src/app/api/reports/annual-xbrl/route.ts; src/lib/annual-report-csv.ts; src/lib/annual-report-xbrl.ts</t>
         </is>
       </c>
     </row>
     <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>Moms-API Skattestyrelsen</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 7, b</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="C29" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E29" s="30" t="inlineStr">
         <is>
           <t>OAuth2 client_credentials mod Skattestyrelsens Moms-API. KUN moms (ingen årsopgørelse/e-indkomst).</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="30" t="inlineStr">
         <is>
           <t>Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1 (momsangivelse) + Bilag 4 (BRUGSVEJLEDNING.md) afsnit 9.3 (indsendelse via SKAT-API) + Bilag 10 (UDBEDRINGSPLAN.md) afsnit 5 (mangel 4 — simuleringstilstand ved manglende credentials).</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G29" s="30" t="inlineStr">
         <is>
           <t>src/lib/vat-submit.ts; src/app/api/vat-report/submit/route.ts; prisma/schema.prisma (VATSubmission)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>Meddelelse om NemHandelsregisteret</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 8</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="C30" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E30" s="30" t="inlineStr">
         <is>
           <t>Virksomhed kan meddele e-faktura-indstillinger (NemHandel/Peppol).</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 16.3 (e-faktura indstillinger).</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="30" t="inlineStr">
         <is>
           <t>src/app/api/company/einvoice-settings/route.ts; src/components/settings/einvoice-settings.tsx</t>
         </is>
       </c>
     </row>
     <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="30" t="inlineStr">
         <is>
           <t>Tilmelding NemHandelsregisteret</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="30" t="inlineStr">
         <is>
           <t>Bilag 2, 9</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="C31" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E31" s="30" t="inlineStr">
         <is>
           <t>Tilmelding via Storecove (Peppol/NemHandel Access Point).</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="30" t="inlineStr">
         <is>
           <t>Bilag 4 (BRUGSVEJLEDNING.md) afsnit 16.3 + Bilag 2 (COMPLIANCE_RAPPORT.md) afsnit 2.1 (Storecove som Access Point) + Bilag 10 (UDBEDRINGSPLAN.md) afsnit 6 (mangel 5 — NemHandel simulering ved manglende AP-aftale).</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="30" t="inlineStr">
         <is>
           <t>src/app/api/company/einvoice-register/route.ts; src/lib/einvoice-sender.ts; src/lib/nemhandel-client.ts; src/lib/storecove-client.ts</t>
         </is>
@@ -3916,13 +4092,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF7030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -3930,220 +4107,221 @@
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>Statusoversigt — AlphaFlow Tjekliste (Version 2.0 — 2026)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>Ark</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>Delvist</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>Nej</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>Ikke relevant</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="29" t="inlineStr">
         <is>
           <t>I alt</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>Krav til anmeldelsen (BEK 98)</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="36" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>Hovedkrav nr. 1 (BEK 97 Bilag 1)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="36" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>Hovedkrav nr. 2 (BEK 97 §7–§8)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="36" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>Hovedkrav nr. 3 (BEK 97 Bilag 2)</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="31" t="n">
         <v>26</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="36" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>I ALT</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="31" t="n">
         <v>76</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="38" t="n">
         <v>83</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>Delvist-opfyldte krav ( krav der afventer afhjælpning — se Bilag 10 UDBEDRINGSPLAN.md):</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>• Hovedkrav nr. 1 — 'Kan ikke ændres/slettes' (Bilag 1, 2, e): Ingen kryptografisk hash-chain på posteringer. AuditLog er 3-niveau uforanderlig. Jf. Bilag 6 RISIKOVURDERING.md R-04.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>• Hovedkrav nr. 1 — 'Bevares uændret' (Bilag 1, 4, a): Samme som ovenfor (ingen hash-chain).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>• Hovedkrav nr. 3 — 'Sende kreditnota i OIOUBL' (Bilag 2, 1, c): Bibliotek understøtter type 381, men intet oprettelses-flow i UI; einvoice-sender hardcoder type 380. Jf. Bilag 1 ANMELDELSESPAKKE.md afsnit 8 punkt 11.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>• Hovedkrav nr. 3 — 'Sende kreditnota i Peppol BIS' (Bilag 2, 2, c): Samme begrænsning som OIOUBL kreditnota.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>• Hovedkrav nr. 3 — 'Automatisk bankintegration' (Bilag 2, 3, b): Tink + Demo er reelle; Nordea/Danske Bank/Jyske Bank er stubs. Jf. Bilag 1 afsnit 8 punkt 12.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>• Hovedkrav nr. 3 — 'PSD2 bankhåndtering' (Bilag 2, 3, c): Consent-flow virker for Tink; sandbox-stubs for øvrige banker.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>Komplet bilagsliste: se Bilag 12 (BILAG_OVERSIGT.md). Lovgrundlag: Lov om bogføring (LOV nr. 700 af 24. maj 2022); BEK nr. 97 af 26. januar 2023; BEK nr. 98 af 26. januar 2023.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A10:F10"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
